--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -932,63 +932,13 @@
     <t xml:space="preserve">Trigger if ≥ 5 tx between €13,500–€14,999 in 2h</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">customer_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> to filter the customer’s past transactions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Current tx &amp; Historical txs (2h window) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 
+    <t xml:space="preserve"> Use customer_id to filter the customer’s past transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current tx &amp; Historical txs (2h window) : 
 -customer_id 
 -timestamp
 -amount</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">R18</t>
@@ -1278,7 +1228,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1313,6 +1263,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1385,7 +1341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1503,6 +1459,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2171,37 +2131,37 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+    <row r="11" s="16" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21" t="n">
+      <c r="F11" s="30"/>
+      <c r="G11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="23" t="s">
+      <c r="K11" s="10"/>
+      <c r="L11" s="13" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2260,7 +2220,7 @@
       <c r="F13" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="31" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="21" t="s">
@@ -2269,7 +2229,7 @@
       <c r="I13" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="32" t="s">
         <v>93</v>
       </c>
       <c r="K13" s="18" t="s">

--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -1410,6 +1410,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1427,10 +1431,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1847,108 +1847,108 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="16" customFormat="true" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="10" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="13"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="17" t="s">
         <v>29</v>
       </c>
       <c r="L3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="19"/>
       <c r="L4" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="18"/>
+      <c r="K5" s="19"/>
       <c r="L5" s="23" t="s">
         <v>44</v>
       </c>
@@ -1988,37 +1988,37 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="19"/>
       <c r="L7" s="23" t="s">
         <v>55</v>
       </c>
@@ -2096,37 +2096,37 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="18"/>
+      <c r="K10" s="19"/>
       <c r="L10" s="23" t="s">
         <v>75</v>
       </c>
@@ -2202,37 +2202,37 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="19" t="s">
         <v>92</v>
       </c>
       <c r="J13" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="19" t="s">
         <v>94</v>
       </c>
       <c r="L13" s="23" t="s">

--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -932,63 +932,13 @@
     <t xml:space="preserve">Trigger if ≥ 5 tx between €13,500–€14,999 in 2h</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">customer_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> to filter the customer’s past transactions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Current tx &amp; Historical txs (2h window) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 
+    <t xml:space="preserve"> Use customer_id to filter the customer’s past transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current tx &amp; Historical txs (2h window) : 
 -customer_id 
 -timestamp
 -amount</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">R18</t>
@@ -1278,7 +1228,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1307,6 +1257,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
@@ -1385,132 +1341,156 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1543,7 +1523,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF3B7D23"/>
+          <fgColor rgb="FF3A7D22"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1593,14 +1573,14 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF3B7D23"/>
+      <rgbColor rgb="FF3A7D22"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -1801,10 +1781,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="33.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="16.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="39.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="39.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="75.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="88.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="49.72"/>
@@ -1887,109 +1867,109 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="16" customFormat="true" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="10" t="s">
         <v>28</v>
       </c>
       <c r="J3" s="13"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="17" t="s">
         <v>29</v>
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" s="16" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="23" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" s="16" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="23" t="s">
+      <c r="K5" s="10"/>
+      <c r="L5" s="15" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2028,180 +2008,180 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="19"/>
       <c r="L7" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" s="16" customFormat="true" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" s="29" customFormat="true" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="13" t="s">
+      <c r="K8" s="25"/>
+      <c r="L8" s="28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" s="29" customFormat="true" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+    <row r="9" s="35" customFormat="true" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="28" t="s">
+      <c r="K9" s="31"/>
+      <c r="L9" s="34" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="18"/>
+      <c r="K10" s="19"/>
       <c r="L10" s="23" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+    <row r="11" s="16" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21" t="n">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="23" t="s">
+      <c r="K11" s="10"/>
+      <c r="L11" s="15" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2242,74 +2222,74 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="19" t="s">
         <v>94</v>
       </c>
       <c r="L13" s="23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" s="16" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+    <row r="14" s="29" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="13" t="s">
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="28" t="s">
         <v>101</v>
       </c>
     </row>

--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t xml:space="preserve">Rule ID</t>
   </si>
@@ -1151,6 +1151,15 @@
 </t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R24 – amount equal, or greate than?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R17 – what severity?</t>
+  </si>
 </sst>
 </file>
 
@@ -1159,7 +1168,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,6 +1235,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1341,7 +1358,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1491,6 +1508,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1773,7 +1798,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.72"/>
@@ -2293,38 +2318,53 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" s="16" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+    <row r="15" s="29" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="15" t="s">
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="38" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -1245,7 +1245,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1286,6 +1286,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1358,7 +1364,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1503,16 +1509,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2176,37 +2190,37 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" s="16" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+    <row r="11" s="29" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12" t="n">
+      <c r="F11" s="36"/>
+      <c r="G11" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="15" t="s">
+      <c r="K11" s="25"/>
+      <c r="L11" s="37" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2265,7 +2279,7 @@
       <c r="F13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="36" t="n">
+      <c r="G13" s="38" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="22" t="s">
@@ -2274,7 +2288,7 @@
       <c r="I13" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="39" t="s">
         <v>93</v>
       </c>
       <c r="K13" s="19" t="s">
@@ -2343,17 +2357,17 @@
       <c r="H15" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="40" t="s">
         <v>105</v>
       </c>
       <c r="J15" s="25"/>
       <c r="K15" s="25"/>
-      <c r="L15" s="38" t="s">
+      <c r="L15" s="37" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="41" t="s">
         <v>107</v>
       </c>
     </row>

--- a/docs/4. HACKATHON_FRAML_RULES.xlsx
+++ b/docs/4. HACKATHON_FRAML_RULES.xlsx
@@ -2224,39 +2224,39 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" s="16" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+    <row r="12" s="29" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="13" t="s">
+      <c r="K12" s="25"/>
+      <c r="L12" s="28" t="s">
         <v>88</v>
       </c>
     </row>
